--- a/py project/rocket/generated_data/initial_sets_index.xlsx
+++ b/py project/rocket/generated_data/initial_sets_index.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>42</v>
+        <v>7026</v>
       </c>
       <c r="E2" t="n">
         <v>50</v>
@@ -495,7 +495,7 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>42</v>
+        <v>8026</v>
       </c>
       <c r="E3" t="n">
         <v>60</v>
@@ -524,7 +524,7 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>42</v>
+        <v>9026</v>
       </c>
       <c r="E4" t="n">
         <v>70</v>
@@ -553,7 +553,7 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>42</v>
+        <v>10026</v>
       </c>
       <c r="E5" t="n">
         <v>80</v>
@@ -566,6 +566,122 @@
       <c r="G5" t="inlineStr">
         <is>
           <t>/home/kkkk24/桌面/attention-GP/py project/rocket/generated_data/initial_sets/rocket_initial_n80.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>rocket</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>90</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>11026</v>
+      </c>
+      <c r="E6" t="n">
+        <v>90</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>rocket_initial_n90.xlsx</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>/home/kkkk24/桌面/attention-GP/py project/rocket/generated_data/initial_sets/rocket_initial_n90.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>rocket</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>12026</v>
+      </c>
+      <c r="E7" t="n">
+        <v>100</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>rocket_initial_n100.xlsx</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>/home/kkkk24/桌面/attention-GP/py project/rocket/generated_data/initial_sets/rocket_initial_n100.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>rocket</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>110</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>13026</v>
+      </c>
+      <c r="E8" t="n">
+        <v>110</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>rocket_initial_n110.xlsx</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>/home/kkkk24/桌面/attention-GP/py project/rocket/generated_data/initial_sets/rocket_initial_n110.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>rocket</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>120</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>14026</v>
+      </c>
+      <c r="E9" t="n">
+        <v>120</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>rocket_initial_n120.xlsx</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>/home/kkkk24/桌面/attention-GP/py project/rocket/generated_data/initial_sets/rocket_initial_n120.xlsx</t>
         </is>
       </c>
     </row>
